--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_metropolitana.xlsx
@@ -399,7 +399,7 @@
         <v>25.06713709218228</v>
       </c>
       <c r="E2">
-        <v>1.775307207945686</v>
+        <v>3.198859459137243</v>
       </c>
     </row>
   </sheetData>
@@ -466,10 +466,10 @@
         <v>27.96915977574395</v>
       </c>
       <c r="F2">
-        <v>1.752583411286179</v>
+        <v>3.832299828864059</v>
       </c>
       <c r="G2">
-        <v>1.909904614657271</v>
+        <v>4.100129095968194</v>
       </c>
     </row>
     <row r="3">
@@ -489,10 +489,10 @@
         <v>26.99500968085476</v>
       </c>
       <c r="F3">
-        <v>1.733322561760367</v>
+        <v>3.706310481988576</v>
       </c>
       <c r="G3">
-        <v>1.91568172128303</v>
+        <v>3.967352101685866</v>
       </c>
     </row>
     <row r="4">
@@ -512,10 +512,10 @@
         <v>25.64879480136777</v>
       </c>
       <c r="F4">
-        <v>1.735185591625168</v>
+        <v>3.528881549738357</v>
       </c>
       <c r="G4">
-        <v>1.918683158322623</v>
+        <v>3.777821102582965</v>
       </c>
     </row>
     <row r="5">
@@ -535,10 +535,10 @@
         <v>24.79903948360599</v>
       </c>
       <c r="F5">
-        <v>1.705488150748485</v>
+        <v>3.285327299229039</v>
       </c>
       <c r="G5">
-        <v>1.887755519183511</v>
+        <v>3.549381614936378</v>
       </c>
     </row>
     <row r="6">
@@ -558,10 +558,10 @@
         <v>26.48753285093164</v>
       </c>
       <c r="F6">
-        <v>1.705057325956374</v>
+        <v>3.240500703165465</v>
       </c>
       <c r="G6">
-        <v>1.798818585453672</v>
+        <v>3.43589360472492</v>
       </c>
     </row>
     <row r="7">
@@ -581,10 +581,10 @@
         <v>25.98468350142434</v>
       </c>
       <c r="F7">
-        <v>1.682033515015993</v>
+        <v>3.121573487239369</v>
       </c>
       <c r="G7">
-        <v>1.782819299211154</v>
+        <v>3.321569364645888</v>
       </c>
     </row>
     <row r="8">
@@ -604,10 +604,10 @@
         <v>25.06713709218228</v>
       </c>
       <c r="F8">
-        <v>1.670470533168663</v>
+        <v>3.003522101338716</v>
       </c>
       <c r="G8">
-        <v>1.775307207945686</v>
+        <v>3.198859459137243</v>
       </c>
     </row>
   </sheetData>
@@ -655,7 +655,7 @@
         <v>23.6543729052743</v>
       </c>
       <c r="D2">
-        <v>1.787418691209721</v>
+        <v>3.096720371558374</v>
       </c>
     </row>
     <row r="3">
@@ -671,7 +671,7 @@
         <v>26.48940901833851</v>
       </c>
       <c r="D3">
-        <v>1.734127214120437</v>
+        <v>3.207545458293819</v>
       </c>
     </row>
     <row r="4">
@@ -687,7 +687,7 @@
         <v>33.82175158388972</v>
       </c>
       <c r="D4">
-        <v>1.896846692547766</v>
+        <v>5.291755149713315</v>
       </c>
     </row>
     <row r="5">
@@ -703,7 +703,7 @@
         <v>29.04165897979891</v>
       </c>
       <c r="D5">
-        <v>1.754189379152719</v>
+        <v>3.575933122365044</v>
       </c>
     </row>
     <row r="6">
@@ -719,7 +719,7 @@
         <v>29.90847467749641</v>
       </c>
       <c r="D6">
-        <v>1.555230465575293</v>
+        <v>2.907764777389454</v>
       </c>
     </row>
     <row r="7">
@@ -735,7 +735,7 @@
         <v>28.19471216882047</v>
       </c>
       <c r="D7">
-        <v>1.739979987992796</v>
+        <v>3.415625638366411</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_metropolitana.xlsx
@@ -393,10 +393,10 @@
         <v>2024</v>
       </c>
       <c r="C2">
+        <v>25.06713709218228</v>
+      </c>
+      <c r="D2">
         <v>31.26114206560697</v>
-      </c>
-      <c r="D2">
-        <v>25.06713709218228</v>
       </c>
       <c r="E2">
         <v>3.198859459137243</v>
@@ -454,16 +454,16 @@
         <v>2018</v>
       </c>
       <c r="B2">
+        <v>30.96463348286845</v>
+      </c>
+      <c r="C2">
+        <v>27.96915977574395</v>
+      </c>
+      <c r="D2">
         <v>26.09399171923384</v>
       </c>
-      <c r="C2">
+      <c r="E2">
         <v>24.38947595536288</v>
-      </c>
-      <c r="D2">
-        <v>30.96463348286845</v>
-      </c>
-      <c r="E2">
-        <v>27.96915977574395</v>
       </c>
       <c r="F2">
         <v>3.832299828864059</v>
@@ -477,16 +477,16 @@
         <v>2019</v>
       </c>
       <c r="B3">
+        <v>30.71165626375393</v>
+      </c>
+      <c r="C3">
+        <v>26.99500968085476</v>
+      </c>
+      <c r="D3">
         <v>26.98100995207131</v>
       </c>
-      <c r="C3">
+      <c r="E3">
         <v>25.20572851537591</v>
-      </c>
-      <c r="D3">
-        <v>30.71165626375393</v>
-      </c>
-      <c r="E3">
-        <v>26.99500968085476</v>
       </c>
       <c r="F3">
         <v>3.706310481988576</v>
@@ -500,16 +500,16 @@
         <v>2020</v>
       </c>
       <c r="B4">
+        <v>29.29313247284859</v>
+      </c>
+      <c r="C4">
+        <v>25.64879480136777</v>
+      </c>
+      <c r="D4">
         <v>28.337590420799</v>
       </c>
-      <c r="C4">
+      <c r="E4">
         <v>26.4702846653136</v>
-      </c>
-      <c r="D4">
-        <v>29.29313247284859</v>
-      </c>
-      <c r="E4">
-        <v>25.64879480136777</v>
       </c>
       <c r="F4">
         <v>3.528881549738357</v>
@@ -523,16 +523,16 @@
         <v>2021</v>
       </c>
       <c r="B5">
+        <v>28.1958714984216</v>
+      </c>
+      <c r="C5">
+        <v>24.79903948360599</v>
+      </c>
+      <c r="D5">
         <v>30.43836759383663</v>
       </c>
-      <c r="C5">
+      <c r="E5">
         <v>28.17392178377881</v>
-      </c>
-      <c r="D5">
-        <v>28.1958714984216</v>
-      </c>
-      <c r="E5">
-        <v>24.79903948360599</v>
       </c>
       <c r="F5">
         <v>3.285327299229039</v>
@@ -546,16 +546,16 @@
         <v>2022</v>
       </c>
       <c r="B6">
+        <v>27.7896259030398</v>
+      </c>
+      <c r="C6">
+        <v>26.48753285093164</v>
+      </c>
+      <c r="D6">
         <v>30.85942857605788</v>
       </c>
-      <c r="C6">
+      <c r="E6">
         <v>29.10451006471316</v>
-      </c>
-      <c r="D6">
-        <v>27.7896259030398</v>
-      </c>
-      <c r="E6">
-        <v>26.48753285093164</v>
       </c>
       <c r="F6">
         <v>3.240500703165465</v>
@@ -569,16 +569,16 @@
         <v>2023</v>
       </c>
       <c r="B7">
+        <v>27.41672147958797</v>
+      </c>
+      <c r="C7">
+        <v>25.98468350142434</v>
+      </c>
+      <c r="D7">
         <v>32.03512600577511</v>
       </c>
-      <c r="C7">
+      <c r="E7">
         <v>30.1062506971493</v>
-      </c>
-      <c r="D7">
-        <v>27.41672147958797</v>
-      </c>
-      <c r="E7">
-        <v>25.98468350142434</v>
       </c>
       <c r="F7">
         <v>3.121573487239369</v>
@@ -592,16 +592,16 @@
         <v>2024</v>
       </c>
       <c r="B8">
+        <v>26.56912786797274</v>
+      </c>
+      <c r="C8">
+        <v>25.06713709218228</v>
+      </c>
+      <c r="D8">
         <v>33.29424476531351</v>
       </c>
-      <c r="C8">
+      <c r="E8">
         <v>31.26114206560697</v>
-      </c>
-      <c r="D8">
-        <v>26.56912786797274</v>
-      </c>
-      <c r="E8">
-        <v>25.06713709218228</v>
       </c>
       <c r="F8">
         <v>3.003522101338716</v>
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B2">
+        <v>23.6543729052743</v>
+      </c>
+      <c r="C2">
         <v>32.29222790615629</v>
-      </c>
-      <c r="C2">
-        <v>23.6543729052743</v>
       </c>
       <c r="D2">
         <v>3.096720371558374</v>
@@ -665,10 +665,10 @@
         </is>
       </c>
       <c r="B3">
+        <v>26.48940901833851</v>
+      </c>
+      <c r="C3">
         <v>31.17648722372051</v>
-      </c>
-      <c r="C3">
-        <v>26.48940901833851</v>
       </c>
       <c r="D3">
         <v>3.207545458293819</v>
@@ -681,10 +681,10 @@
         </is>
       </c>
       <c r="B4">
+        <v>33.82175158388972</v>
+      </c>
+      <c r="C4">
         <v>18.89732180927108</v>
-      </c>
-      <c r="C4">
-        <v>33.82175158388972</v>
       </c>
       <c r="D4">
         <v>5.291755149713315</v>
@@ -697,10 +697,10 @@
         </is>
       </c>
       <c r="B5">
+        <v>29.04165897979891</v>
+      </c>
+      <c r="C5">
         <v>27.9647288073056</v>
-      </c>
-      <c r="C5">
-        <v>29.04165897979891</v>
       </c>
       <c r="D5">
         <v>3.575933122365044</v>
@@ -713,10 +713,10 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.90847467749641</v>
+      </c>
+      <c r="C6">
         <v>34.39067725752508</v>
-      </c>
-      <c r="C6">
-        <v>29.90847467749641</v>
       </c>
       <c r="D6">
         <v>2.907764777389454</v>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B7">
+        <v>28.19471216882047</v>
+      </c>
+      <c r="C7">
         <v>29.27721319243491</v>
-      </c>
-      <c r="C7">
-        <v>28.19471216882047</v>
       </c>
       <c r="D7">
         <v>3.415625638366411</v>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_metropolitana.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t xml:space="preserve">Territorio</t>
   </si>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-27 21:11</t>
+    <t xml:space="preserve">2026-07-30 18:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -59,16 +59,25 @@
     <t xml:space="preserve">Imagen asociada</t>
   </si>
   <si>
-    <t xml:space="preserve"/>
+    <t xml:space="preserve">plot_regional_d_otrasrel_a_2024_metropolitana.png</t>
   </si>
   <si>
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
+    <t xml:space="preserve">Otras relaciones demograficas</t>
+  </si>
+  <si>
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
+    <t xml:space="preserve">Region de Metropolitana</t>
+  </si>
+  <si>
     <t xml:space="preserve">Año</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024</t>
   </si>
   <si>
     <t xml:space="preserve">year</t>
@@ -569,23 +578,23 @@
         <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -610,25 +619,25 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2">
@@ -812,7 +821,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
@@ -826,7 +835,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>23.65</v>
@@ -840,7 +849,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>26.49</v>
@@ -854,7 +863,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>33.82</v>
@@ -868,7 +877,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>29.04</v>
@@ -882,7 +891,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>29.91</v>
@@ -896,7 +905,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>28.19</v>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_metropolitana.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 18:34</t>
+    <t xml:space="preserve">2026-08-07 07:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_metropolitana.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-07 07:10</t>
+    <t xml:space="preserve">2026-08-17 16:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_metropolitana.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 16:39</t>
+    <t xml:space="preserve">2026-08-19 15:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_metropolitana.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 15:03</t>
+    <t xml:space="preserve">2026-08-28 11:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_metropolitana.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:11</t>
+    <t xml:space="preserve">2026-09-04 20:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_metropolitana.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2024_metropolitana.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-04 20:42</t>
+    <t xml:space="preserve">2026-09-06 17:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
